--- a/data/trans_dic/ProbViv_temp-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,67; 38,41</t>
+          <t>30,04; 38,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,85; 30,97</t>
+          <t>21,8; 31,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 33,67</t>
+          <t>26,81; 33,32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,14; 40,29</t>
+          <t>15,38; 40,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,72; 43,95</t>
+          <t>38,55; 44,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,27; 40,7</t>
+          <t>23,61; 40,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,64; 36,3</t>
+          <t>28,35; 36,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 31,64</t>
+          <t>11,5; 31,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 31,86</t>
+          <t>18,92; 31,89</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,07; 51,89</t>
+          <t>44,74; 52,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,28; 62,97</t>
+          <t>49,3; 62,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,32; 56,57</t>
+          <t>48,6; 56,67</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,03; 39,9</t>
+          <t>28,49; 40,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,37; 41,33</t>
+          <t>30,99; 41,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,85</t>
+          <t>32,72; 40,09</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>194918; 244074</t>
+          <t>190897; 242090</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>158452; 224649</t>
+          <t>158141; 226115</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>363537; 458170</t>
+          <t>364800; 453385</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>192582; 480601</t>
+          <t>183496; 478744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>371230; 421298</t>
+          <t>369554; 422868</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>522197; 875743</t>
+          <t>507989; 880972</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>201786; 255791</t>
+          <t>199760; 257119</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>109417; 295281</t>
+          <t>107299; 293191</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>300898; 521879</t>
+          <t>309846; 522327</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>417682; 480962</t>
+          <t>414706; 483192</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>539567; 689525</t>
+          <t>539813; 679446</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>977003; 1143797</t>
+          <t>982539; 1145816</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>969935; 1380426</t>
+          <t>985624; 1385169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1127339; 1534209</t>
+          <t>1150352; 1537056</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2314614; 2858358</t>
+          <t>2346364; 2875222</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,04; 38,1</t>
+          <t>32,26; 39,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 31,17</t>
+          <t>28,03; 33,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,81; 33,32</t>
+          <t>30,97; 35,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,38; 40,13</t>
+          <t>36,99; 43,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,55; 44,11</t>
+          <t>39,71; 45,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,61; 40,95</t>
+          <t>39,26; 43,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,35; 36,49</t>
+          <t>28,6; 36,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 31,41</t>
+          <t>30,62; 36,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 31,89</t>
+          <t>30,81; 35,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,74; 52,13</t>
+          <t>48,15; 55,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,3; 62,05</t>
+          <t>49,71; 55,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,6; 56,67</t>
+          <t>49,86; 54,16</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,49; 40,04</t>
+          <t>38,93; 42,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,4</t>
+          <t>39,78; 42,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 40,09</t>
+          <t>39,82; 42,08</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>218387</t>
+          <t>247229</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>201505</t>
+          <t>226496</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419893</t>
+          <t>473725</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>190897; 242090</t>
+          <t>222849; 273759</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>158141; 226115</t>
+          <t>205798; 247690</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>364800; 453385</t>
+          <t>441268; 512048</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>426083</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>395674</t>
+          <t>455019</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>764777</t>
+          <t>881103</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>183496; 478744</t>
+          <t>387945; 459491</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>369554; 422868</t>
+          <t>425508; 483693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>507989; 880972</t>
+          <t>832443; 930841</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>226272</t>
+          <t>258241</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>220607</t>
+          <t>271888</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446879</t>
+          <t>530129</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>199760; 257119</t>
+          <t>229649; 289330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107299; 293191</t>
+          <t>248692; 299399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>309846; 522327</t>
+          <t>497640; 569316</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>450752</t>
+          <t>509955</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>585703</t>
+          <t>587094</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1036455</t>
+          <t>1097050</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>414706; 483192</t>
+          <t>476695; 547011</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>539813; 679446</t>
+          <t>556292; 618324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>982539; 1145816</t>
+          <t>1051660; 1142197</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1264515</t>
+          <t>1441509</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1403489</t>
+          <t>1540497</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2668004</t>
+          <t>2982006</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>985624; 1385169</t>
+          <t>1375418; 1505660</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1150352; 1537056</t>
+          <t>1486416; 1595252</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2346364; 2875222</t>
+          <t>2894695; 3059329</t>
         </is>
       </c>
     </row>
